--- a/ksoft/docs/records/Business_Unit_Records.xlsx
+++ b/ksoft/docs/records/Business_Unit_Records.xlsx
@@ -1498,13 +1498,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6B58234-2B4B-403D-B5F4-1E80EF6DA49B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9184C4B7-8144-43BD-8309-10157FB3F0E4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9054EC3-C8AD-4E71-9D67-71EE036AFDC2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9550B9D-644A-458D-81DE-BC65DC67D6A0}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB135FF6-A7C6-4C59-839B-A32AC210EB0E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63A4E248-D6DE-4442-8348-48735181E39C}"/>
 </file>
--- a/ksoft/docs/records/Business_Unit_Records.xlsx
+++ b/ksoft/docs/records/Business_Unit_Records.xlsx
@@ -1498,13 +1498,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9184C4B7-8144-43BD-8309-10157FB3F0E4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6B58234-2B4B-403D-B5F4-1E80EF6DA49B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9550B9D-644A-458D-81DE-BC65DC67D6A0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9054EC3-C8AD-4E71-9D67-71EE036AFDC2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63A4E248-D6DE-4442-8348-48735181E39C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB135FF6-A7C6-4C59-839B-A32AC210EB0E}"/>
 </file>